--- a/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
@@ -766,10 +766,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -821,22 +821,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -991,22 +991,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>05/14/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -1108,22 +1108,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>05/14/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -1225,22 +1225,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>05/14/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -1342,22 +1342,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>05/14/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1459,22 +1459,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>Allwell - All States (Centene)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Allwell - All States (Centene)</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -1576,22 +1576,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>05/20/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>05/20/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1701,22 +1701,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>05/20/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>05/20/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>05/20/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>05/20/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -1951,22 +1951,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>05/22/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>05/22/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -2068,22 +2068,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>05/22/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>05/22/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -2185,22 +2185,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>05/22/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Mercy Care RBHA</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>05/22/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>05/22/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Mercy Care RBHA</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>05/22/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -2427,22 +2427,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>05/29/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>05/29/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -2540,22 +2540,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>05/29/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>05/29/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -2653,22 +2653,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>05/27/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -2766,22 +2766,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>05/27/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2895,22 +2895,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>05/27/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -3004,22 +3004,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>05/27/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -3113,22 +3113,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>ChampVA - HAC</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>05/01/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -3222,22 +3222,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>ChampVA - HAC</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>05/01/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -3331,22 +3331,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -3444,22 +3444,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -3561,22 +3561,22 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -3680,22 +3680,22 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -3799,22 +3799,22 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -3918,22 +3918,22 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -4033,22 +4033,22 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Bankers Life Colonial Penn Life</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -4146,22 +4146,22 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Bankers Life Colonial Penn Life</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -4263,22 +4263,22 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -4382,22 +4382,22 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -4501,22 +4501,22 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -4620,22 +4620,22 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -4739,22 +4739,22 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
+          <t>05/15/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>05/15/2026</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -4858,22 +4858,22 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
+          <t>05/15/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>05/15/2026</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -4977,22 +4977,22 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
+          <t>05/28/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>05/28/2026</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -5092,22 +5092,22 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
           <t>Banner Health Physician Hospital Organization Plan Administration</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Banner Health Physician Hospital Organization Plan Administration</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -5201,22 +5201,22 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
           <t>Banner Health Physician Hospital Organization Plan Administration</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Banner Health Physician Hospital Organization Plan Administration</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -5310,22 +5310,22 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
+          <t>05/19/2026</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
           <t>Arizona Priority Care Plus</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Arizona Priority Care Plus</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>05/19/2026</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -5423,22 +5423,22 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
+          <t>05/19/2026</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
           <t>Arizona Priority Care Plus</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Arizona Priority Care Plus</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>05/19/2026</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -5536,22 +5536,22 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>05/01/2026</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -5645,22 +5645,22 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>05/01/2026</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -5754,22 +5754,22 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -5863,22 +5863,22 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -5980,22 +5980,22 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
+          <t>05/12/2026</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>05/12/2026</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
@@ -6105,22 +6105,22 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
+          <t>05/12/2026</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>05/12/2026</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -6222,22 +6222,22 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
@@ -6333,22 +6333,22 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
@@ -6444,22 +6444,22 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
+          <t>05/15/2026</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>05/15/2026</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -6662,22 +6662,22 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
+          <t>05/15/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>05/15/2026</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -6773,22 +6773,22 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
+          <t>05/22/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>05/22/2026</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -6888,22 +6888,22 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
+          <t>05/22/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>05/22/2026</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
@@ -7003,22 +7003,22 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
+          <t>05/28/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>05/28/2026</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
@@ -7114,22 +7114,22 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
+          <t>05/28/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>05/28/2026</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
@@ -7225,22 +7225,22 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
+          <t>05/28/2026</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
           <t>EMI Health (Educators Mutual - EMIA)</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>EMI Health (Educators Mutual - EMIA)</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>05/28/2026</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
@@ -7332,22 +7332,22 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
+          <t>05/28/2026</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
           <t>EMI Health (Educators Mutual - EMIA)</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>EMI Health (Educators Mutual - EMIA)</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>05/28/2026</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
@@ -7439,22 +7439,22 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
+          <t>05/29/2026</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="H58" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>05/29/2026</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -7575,10 +7575,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -7630,22 +7630,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -7800,22 +7800,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>05/15/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>LIEN 03</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>05/15/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -7933,22 +7933,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>05/18/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>05/18/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -8058,22 +8058,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>05/18/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>05/18/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -8191,22 +8191,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>05/21/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Molina Complete Care of Arizona (Magellan Complete Care AZ)</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>05/21/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -8320,22 +8320,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>05/22/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>05/22/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -8441,22 +8441,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>05/26/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>05/26/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -8566,22 +8566,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>Banner Medicare Advantage Prime HMO (BMAH)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Banner Medicare Advantage Prime HMO (BMAH)</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -8683,22 +8683,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>05/26/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>Arizona Complete Health (Centene)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>05/26/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -8812,22 +8812,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -8933,22 +8933,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>05/18/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>Oscar Health</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Oscar Health</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>05/18/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -9054,22 +9054,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>05/19/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>05/19/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -9175,22 +9175,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>05/28/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>05/28/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -9300,22 +9300,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -9417,22 +9417,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -9542,22 +9542,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -9665,22 +9665,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -9794,22 +9794,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>Tricare for Life (All Regions)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Tricare for Life (All Regions)</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>05/14/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -9917,22 +9917,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Aetna Life &amp; Casualty Company</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>05/14/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -10038,22 +10038,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>Aetna Life &amp; Casualty Company</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>05/14/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -10159,22 +10159,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>05/18/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>05/18/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -10276,22 +10276,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>05/19/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>05/19/2026</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -10397,22 +10397,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>05/26/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Physicians Mutual Insurance Company - ENS</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>05/26/2026</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -10518,22 +10518,22 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>05/26/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>Tricare for Life (All Regions)</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>05/26/2026</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -10635,22 +10635,22 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>05/28/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>ACE MEDICARE SUPPLEMENTAL</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>05/28/2026</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -10764,22 +10764,22 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>05/29/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>05/29/2026</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -10889,22 +10889,22 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>Devoted Health Plan</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Devoted Health Plan</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -11006,22 +11006,22 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>05/01/2026</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -11123,22 +11123,22 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>05/01/2026</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -11240,22 +11240,22 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -11365,22 +11365,22 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Banner University Family Care - Arizona Long Term Care System</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -11486,22 +11486,22 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -11736,22 +11736,22 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -11865,22 +11865,22 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -11976,22 +11976,22 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -12124,10 +12124,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -12341,22 +12341,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -12466,22 +12466,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -12587,22 +12587,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -12716,22 +12716,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -12837,22 +12837,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -12962,22 +12962,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -13087,22 +13087,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -13220,22 +13220,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -13345,22 +13345,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -13478,22 +13478,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>05/18/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Aetna Legacy</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>05/18/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -13613,22 +13613,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>05/18/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Aetna Legacy</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>05/18/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -13748,22 +13748,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>05/18/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Aetna Legacy</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>05/18/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -13875,22 +13875,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>05/18/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Aetna Legacy</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>05/18/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -14006,22 +14006,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>05/18/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Aetna Legacy</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>05/18/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -14145,22 +14145,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>05/18/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Aetna Legacy</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>05/18/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -14276,22 +14276,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>05/18/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Aetna Legacy</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>05/18/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -14403,22 +14403,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -14532,22 +14532,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -14665,22 +14665,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -14798,22 +14798,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -14927,22 +14927,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -15060,22 +15060,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -15197,22 +15197,22 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -15326,22 +15326,22 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -15445,22 +15445,22 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -15564,22 +15564,22 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -15683,22 +15683,22 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -15810,22 +15810,22 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -15933,22 +15933,22 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -16056,22 +16056,22 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Gold Kidney Health Plan</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -16200,10 +16200,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -16255,22 +16255,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -16425,22 +16425,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>05/14/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -16546,22 +16546,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>05/18/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>05/18/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -16671,22 +16671,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>05/18/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>05/18/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -16796,22 +16796,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>05/15/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>Allwell - All States (Centene)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Allwell - All States (Centene)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>05/15/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -16925,22 +16925,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>05/21/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>05/21/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>05/26/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>05/26/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -17163,22 +17163,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>05/27/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -17288,22 +17288,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>05/01/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -17409,22 +17409,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -17542,22 +17542,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -17675,22 +17675,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>05/14/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -17792,22 +17792,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Oscar Health</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Oscar Health</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>05/14/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -17905,22 +17905,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>05/14/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -18022,22 +18022,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>05/14/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -18139,22 +18139,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>05/01/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -18256,22 +18256,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -18381,22 +18381,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Tricare for Life (All Regions)</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -18494,22 +18494,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -18611,22 +18611,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>05/15/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>Tricare for Life (All Regions)</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>05/15/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -18736,22 +18736,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>05/29/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>05/29/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -18855,22 +18855,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>Devoted Health Plan</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Devoted Health Plan</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -18972,22 +18972,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>UHC Group Medicare Advantage</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -19085,22 +19085,22 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -19202,22 +19202,22 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -19331,22 +19331,22 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -19464,22 +19464,22 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -19593,22 +19593,22 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -19722,22 +19722,22 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -19847,22 +19847,22 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -19987,10 +19987,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -20042,22 +20042,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -20212,22 +20212,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>05/21/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>05/21/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -20333,22 +20333,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>05/21/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>05/21/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -20454,22 +20454,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>05/21/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>05/21/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -20571,22 +20571,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>05/21/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>05/21/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -20688,22 +20688,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>05/21/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>05/21/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -20805,22 +20805,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>05/21/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>05/21/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -20930,22 +20930,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>05/21/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>05/21/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -21055,22 +21055,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>05/21/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>05/21/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -21172,22 +21172,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>05/26/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>05/26/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -21293,22 +21293,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>05/26/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>05/26/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -21414,22 +21414,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>05/27/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -21539,22 +21539,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>05/27/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -21664,22 +21664,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -21781,22 +21781,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -21902,22 +21902,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Aetna</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -22023,22 +22023,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Tricare for Life (All Regions)</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -22144,22 +22144,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Tricare for Life (All Regions)</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -22265,22 +22265,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Tricare for Life (All Regions)</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -22390,22 +22390,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>05/12/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>05/12/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -22507,22 +22507,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Aetna Legacy</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -22626,22 +22626,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>Aetna Legacy</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -22745,22 +22745,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Aetna Legacy</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -22860,22 +22860,22 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>05/19/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>MediCo Insurance Company</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>05/19/2026</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -22981,22 +22981,22 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>05/19/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>MediCo Insurance Company</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>05/19/2026</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -23102,22 +23102,22 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>05/19/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>MediCo Insurance Company</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>05/19/2026</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -23223,22 +23223,22 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>05/20/2026</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>05/20/2026</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -23336,22 +23336,22 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>Arizona Priority Care Plus</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Arizona Priority Care Plus</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -23449,22 +23449,22 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
           <t>Arizona Priority Care Plus</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Arizona Priority Care Plus</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -23562,22 +23562,22 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
           <t>Arizona Priority Care Plus</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Arizona Priority Care Plus</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -23675,22 +23675,22 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -23788,22 +23788,22 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -23901,22 +23901,22 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -24022,22 +24022,22 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
+          <t>05/12/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>05/12/2026</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -24147,22 +24147,22 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
+          <t>05/12/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>05/12/2026</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -24272,22 +24272,22 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -24401,22 +24401,22 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -24530,22 +24530,22 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
+          <t>05/13/2026</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -24651,22 +24651,22 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -24766,22 +24766,22 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -24881,22 +24881,22 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>United HealthCare Dual Complete</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">

--- a/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI17" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ17" s="5" t="n">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="AI45" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ45" s="5" t="n">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="AI46" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ46" s="5" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="AI4" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ4" s="5" t="n">
@@ -8893,26 +8893,26 @@
       <c r="B9" s="3" t="n"/>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="5" t="n">
-        <v>561859042</v>
+        <v>559750877</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>HF547456904</t>
+          <t>HF400854650</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>05/26/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Arizona Complete Health (Centene)</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Arizona Complete Health (Centene)</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -8931,7 +8931,7 @@
         <v/>
       </c>
       <c r="M9" s="7" t="n">
-        <v>46288</v>
+        <v>46281</v>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>AZ COMPLETE</t>
+          <t>TRIWEST</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
@@ -8964,14 +8964,14 @@
       </c>
       <c r="W9" s="6" t="inlineStr">
         <is>
-          <t>06/17/2026</t>
+          <t>06/11/2026</t>
         </is>
       </c>
       <c r="X9" s="8" t="n">
         <v>36353.8</v>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="Z9" s="6" t="inlineStr">
         <is>
@@ -8983,30 +8983,22 @@
           <t>M961</t>
         </is>
       </c>
-      <c r="AB9" s="6" t="inlineStr">
-        <is>
-          <t>M5416</t>
-        </is>
-      </c>
-      <c r="AC9" s="6" t="inlineStr">
-        <is>
-          <t>M5116</t>
-        </is>
-      </c>
+      <c r="AB9" s="6" t="n"/>
+      <c r="AC9" s="6" t="n"/>
       <c r="AD9" s="5" t="n"/>
       <c r="AE9" s="6" t="inlineStr">
         <is>
-          <t>BARCOME, MARYBETH</t>
+          <t>LUKE, TIMOTHY</t>
         </is>
       </c>
       <c r="AF9" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP Prescott Valley</t>
         </is>
       </c>
       <c r="AG9" s="6" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>05/20/2026</t>
         </is>
       </c>
       <c r="AH9" s="6" t="inlineStr">
@@ -9014,9 +9006,13 @@
           <t>DME</t>
         </is>
       </c>
-      <c r="AI9" s="9" t="n"/>
+      <c r="AI9" s="9" t="inlineStr">
+        <is>
+          <t>This payer name is on 2 carrier rows in the reference (VETERANS ADMIN (VA CCN) 180 days, and TRIWEST 120 days). The shorter TRIWEST window is applied - confirm which programme the claim belongs to before relying on the longer one.</t>
+        </is>
+      </c>
       <c r="AJ9" s="5" t="n">
-        <v>395</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10">
@@ -9024,26 +9020,26 @@
       <c r="B10" s="3" t="n"/>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="5" t="n">
-        <v>559740566</v>
+        <v>561859042</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>HF513154140</t>
+          <t>HF547456904</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
+          <t>Arizona Complete Health (Centene)</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
+          <t>Arizona Complete Health (Centene)</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -9062,16 +9058,16 @@
         <v/>
       </c>
       <c r="M10" s="7" t="n">
-        <v>46326</v>
+        <v>46288</v>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>180 days</t>
+          <t>120 days</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>MERCY CARE MEDICAID</t>
+          <t>AZ COMPLETE</t>
         </is>
       </c>
       <c r="P10" s="6" t="inlineStr">
@@ -9095,14 +9091,14 @@
       </c>
       <c r="W10" s="6" t="inlineStr">
         <is>
-          <t>05/27/2026</t>
+          <t>06/17/2026</t>
         </is>
       </c>
       <c r="X10" s="8" t="n">
         <v>36353.8</v>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="Z10" s="6" t="inlineStr">
         <is>
@@ -9114,22 +9110,30 @@
           <t>M961</t>
         </is>
       </c>
-      <c r="AB10" s="6" t="n"/>
-      <c r="AC10" s="6" t="n"/>
+      <c r="AB10" s="6" t="inlineStr">
+        <is>
+          <t>M5416</t>
+        </is>
+      </c>
+      <c r="AC10" s="6" t="inlineStr">
+        <is>
+          <t>M5116</t>
+        </is>
+      </c>
       <c r="AD10" s="5" t="n"/>
       <c r="AE10" s="6" t="inlineStr">
         <is>
-          <t>TONDINI, JENISE</t>
+          <t>BARCOME, MARYBETH</t>
         </is>
       </c>
       <c r="AF10" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Goodyear</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG10" s="6" t="inlineStr">
         <is>
-          <t>05/20/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="AH10" s="6" t="inlineStr">
@@ -9139,7 +9143,7 @@
       </c>
       <c r="AI10" s="9" t="n"/>
       <c r="AJ10" s="5" t="n">
-        <v>285</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11">
@@ -9147,26 +9151,26 @@
       <c r="B11" s="3" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="5" t="n">
-        <v>561880706</v>
+        <v>559740566</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>HF551547091</t>
+          <t>HF513154140</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>05/18/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Oscar Health</t>
+          <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Oscar Health</t>
+          <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -9185,7 +9189,7 @@
         <v/>
       </c>
       <c r="M11" s="7" t="n">
-        <v>46340</v>
+        <v>46326</v>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
@@ -9194,7 +9198,7 @@
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>OSCAR HEALTH</t>
+          <t>MERCY CARE MEDICAID</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
@@ -9205,10 +9209,10 @@
       <c r="Q11" s="6" t="n"/>
       <c r="R11" s="6" t="n"/>
       <c r="S11" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>72707.60000000001</v>
+        <v>36353.8</v>
       </c>
       <c r="U11" s="8" t="n">
         <v>0</v>
@@ -9218,14 +9222,14 @@
       </c>
       <c r="W11" s="6" t="inlineStr">
         <is>
-          <t>06/17/2026</t>
+          <t>05/27/2026</t>
         </is>
       </c>
       <c r="X11" s="8" t="n">
-        <v>72707.60000000001</v>
+        <v>36353.8</v>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="Z11" s="6" t="inlineStr">
         <is>
@@ -9234,7 +9238,7 @@
       </c>
       <c r="AA11" s="6" t="inlineStr">
         <is>
-          <t>G90523</t>
+          <t>M961</t>
         </is>
       </c>
       <c r="AB11" s="6" t="n"/>
@@ -9242,17 +9246,17 @@
       <c r="AD11" s="5" t="n"/>
       <c r="AE11" s="6" t="inlineStr">
         <is>
-          <t>Van Dyke, Sandra</t>
+          <t>TONDINI, JENISE</t>
         </is>
       </c>
       <c r="AF11" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - Goodyear</t>
         </is>
       </c>
       <c r="AG11" s="6" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>05/20/2026</t>
         </is>
       </c>
       <c r="AH11" s="6" t="inlineStr">
@@ -9262,7 +9266,7 @@
       </c>
       <c r="AI11" s="9" t="n"/>
       <c r="AJ11" s="5" t="n">
-        <v>396</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -9270,26 +9274,26 @@
       <c r="B12" s="3" t="n"/>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="5" t="n">
-        <v>559750877</v>
+        <v>561880706</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>HF400854650</t>
+          <t>HF551547091</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>05/18/2026</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Oscar Health</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Oscar Health</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -9308,7 +9312,7 @@
         <v/>
       </c>
       <c r="M12" s="7" t="n">
-        <v>46341</v>
+        <v>46340</v>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
@@ -9317,7 +9321,7 @@
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>VETERANS ADMIN (VA CCN)</t>
+          <t>OSCAR HEALTH</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
@@ -9328,10 +9332,10 @@
       <c r="Q12" s="6" t="n"/>
       <c r="R12" s="6" t="n"/>
       <c r="S12" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>36353.8</v>
+        <v>72707.60000000001</v>
       </c>
       <c r="U12" s="8" t="n">
         <v>0</v>
@@ -9341,14 +9345,14 @@
       </c>
       <c r="W12" s="6" t="inlineStr">
         <is>
-          <t>06/11/2026</t>
+          <t>06/17/2026</t>
         </is>
       </c>
       <c r="X12" s="8" t="n">
-        <v>36353.8</v>
+        <v>72707.60000000001</v>
       </c>
       <c r="Y12" s="5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z12" s="6" t="inlineStr">
         <is>
@@ -9357,7 +9361,7 @@
       </c>
       <c r="AA12" s="6" t="inlineStr">
         <is>
-          <t>M961</t>
+          <t>G90523</t>
         </is>
       </c>
       <c r="AB12" s="6" t="n"/>
@@ -9365,17 +9369,17 @@
       <c r="AD12" s="5" t="n"/>
       <c r="AE12" s="6" t="inlineStr">
         <is>
-          <t>LUKE, TIMOTHY</t>
+          <t>Van Dyke, Sandra</t>
         </is>
       </c>
       <c r="AF12" s="6" t="inlineStr">
         <is>
-          <t>ASAP Prescott Valley</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG12" s="6" t="inlineStr">
         <is>
-          <t>05/20/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="AH12" s="6" t="inlineStr">
@@ -9385,7 +9389,7 @@
       </c>
       <c r="AI12" s="9" t="n"/>
       <c r="AJ12" s="5" t="n">
-        <v>512</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13">
@@ -11607,7 +11611,7 @@
       </c>
       <c r="AI30" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ30" s="5" t="n">
@@ -11732,7 +11736,11 @@
           <t>DME</t>
         </is>
       </c>
-      <c r="AI31" s="9" t="n"/>
+      <c r="AI31" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ31" s="5" t="n">
         <v>151</v>
       </c>
@@ -12115,7 +12123,7 @@
       </c>
       <c r="AI34" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ34" s="5" t="n">
@@ -14832,7 +14840,7 @@
       </c>
       <c r="AI18" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ18" s="5" t="n">
@@ -14967,7 +14975,7 @@
       </c>
       <c r="AI19" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ19" s="5" t="n">
@@ -15102,7 +15110,7 @@
       </c>
       <c r="AI20" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ20" s="5" t="n">
@@ -15233,7 +15241,7 @@
       </c>
       <c r="AI21" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ21" s="5" t="n">
@@ -15368,7 +15376,7 @@
       </c>
       <c r="AI22" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ22" s="5" t="n">
@@ -15507,7 +15515,7 @@
       </c>
       <c r="AI23" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ23" s="5" t="n">
@@ -15638,7 +15646,7 @@
       </c>
       <c r="AI24" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ24" s="5" t="n">
@@ -16880,7 +16888,11 @@
           <t>ORTHO</t>
         </is>
       </c>
-      <c r="AI2" s="9" t="n"/>
+      <c r="AI2" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ2" s="5" t="n">
         <v>699</v>
       </c>
@@ -17517,7 +17529,11 @@
           <t>ORTHO</t>
         </is>
       </c>
-      <c r="AI7" s="9" t="n"/>
+      <c r="AI7" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ7" s="5" t="n">
         <v>984</v>
       </c>
@@ -17765,7 +17781,7 @@
       </c>
       <c r="AI9" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ9" s="5" t="n">
@@ -17900,7 +17916,7 @@
       </c>
       <c r="AI10" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ10" s="5" t="n">
@@ -18035,7 +18051,7 @@
       </c>
       <c r="AI11" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ11" s="5" t="n">
@@ -18047,11 +18063,11 @@
       <c r="B12" s="3" t="n"/>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="5" t="n">
-        <v>559655054</v>
+        <v>559611258</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>HF537452337</t>
+          <t>HF400854650</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -18061,12 +18077,12 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Aetna</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Aetna</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -18076,7 +18092,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>63047</t>
+          <t>63685</t>
         </is>
       </c>
       <c r="K12" s="4" t="n"/>
@@ -18094,7 +18110,7 @@
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>AETNA</t>
+          <t>TRIWEST</t>
         </is>
       </c>
       <c r="P12" s="6" t="n"/>
@@ -18104,7 +18120,7 @@
         <v>1</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>7623.07</v>
+        <v>2493.33</v>
       </c>
       <c r="U12" s="8" t="n">
         <v>0</v>
@@ -18112,21 +18128,25 @@
       <c r="V12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W12" s="6" t="n"/>
+      <c r="W12" s="6" t="inlineStr">
+        <is>
+          <t>06/11/2026</t>
+        </is>
+      </c>
       <c r="X12" s="8" t="n">
-        <v>7623.07</v>
+        <v>2493.33</v>
       </c>
       <c r="Y12" s="5" t="n">
         <v>86</v>
       </c>
       <c r="Z12" s="6" t="inlineStr">
         <is>
-          <t>M48062</t>
+          <t>M961</t>
         </is>
       </c>
       <c r="AA12" s="6" t="inlineStr">
         <is>
-          <t>M5416</t>
+          <t>T85122D</t>
         </is>
       </c>
       <c r="AB12" s="6" t="n"/>
@@ -18154,11 +18174,11 @@
       </c>
       <c r="AI12" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>This payer name is on 2 carrier rows in the reference (VETERANS ADMIN (VA CCN) 180 days, and TRIWEST 120 days). The shorter TRIWEST window is applied - confirm which programme the claim belongs to before relying on the longer one.</t>
         </is>
       </c>
       <c r="AJ12" s="5" t="n">
-        <v>1032</v>
+        <v>799</v>
       </c>
     </row>
     <row r="13">
@@ -18166,11 +18186,11 @@
       <c r="B13" s="3" t="n"/>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="5" t="n">
-        <v>559248529</v>
+        <v>559611258</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>HF551547091</t>
+          <t>HF400854650</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -18180,12 +18200,12 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Oscar Health</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Oscar Health</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -18195,7 +18215,7 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>63685</t>
+          <t>63655</t>
         </is>
       </c>
       <c r="K13" s="4" t="n"/>
@@ -18204,16 +18224,16 @@
         <v/>
       </c>
       <c r="M13" s="7" t="n">
-        <v>46336</v>
+        <v>46276</v>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>180 days</t>
+          <t>120 days</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>OSCAR HEALTH</t>
+          <t>TRIWEST</t>
         </is>
       </c>
       <c r="P13" s="6" t="n"/>
@@ -18223,7 +18243,7 @@
         <v>1</v>
       </c>
       <c r="T13" s="8" t="n">
-        <v>2493.33</v>
+        <v>5784.24</v>
       </c>
       <c r="U13" s="8" t="n">
         <v>0</v>
@@ -18233,37 +18253,41 @@
       </c>
       <c r="W13" s="6" t="inlineStr">
         <is>
-          <t>05/28/2026</t>
+          <t>06/11/2026</t>
         </is>
       </c>
       <c r="X13" s="8" t="n">
-        <v>2493.33</v>
+        <v>5784.24</v>
       </c>
       <c r="Y13" s="5" t="n">
         <v>86</v>
       </c>
       <c r="Z13" s="6" t="inlineStr">
         <is>
-          <t>G90523</t>
-        </is>
-      </c>
-      <c r="AA13" s="6" t="n"/>
+          <t>M961</t>
+        </is>
+      </c>
+      <c r="AA13" s="6" t="inlineStr">
+        <is>
+          <t>T85122D</t>
+        </is>
+      </c>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
       <c r="AD13" s="5" t="n"/>
       <c r="AE13" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>LUKE, TIMOTHY</t>
         </is>
       </c>
       <c r="AF13" s="6" t="inlineStr">
         <is>
-          <t>Premier Endoscopy Center, LLC</t>
+          <t>ASAP Surgery Centers North Valley LLC</t>
         </is>
       </c>
       <c r="AG13" s="6" t="inlineStr">
         <is>
-          <t>05/15/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="AH13" s="6" t="inlineStr">
@@ -18271,9 +18295,13 @@
           <t>ORTHO</t>
         </is>
       </c>
-      <c r="AI13" s="9" t="n"/>
+      <c r="AI13" s="9" t="inlineStr">
+        <is>
+          <t>This payer name is on 2 carrier rows in the reference (VETERANS ADMIN (VA CCN) 180 days, and TRIWEST 120 days). The shorter TRIWEST window is applied - confirm which programme the claim belongs to before relying on the longer one.</t>
+        </is>
+      </c>
       <c r="AJ13" s="5" t="n">
-        <v>177</v>
+        <v>800</v>
       </c>
     </row>
     <row r="14">
@@ -18281,11 +18309,11 @@
       <c r="B14" s="3" t="n"/>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="5" t="n">
-        <v>559611258</v>
+        <v>559655054</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>HF400854650</t>
+          <t>HF537452337</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -18295,12 +18323,12 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Aetna</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Aetna</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -18310,7 +18338,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>63685</t>
+          <t>63047</t>
         </is>
       </c>
       <c r="K14" s="4" t="n"/>
@@ -18319,16 +18347,16 @@
         <v/>
       </c>
       <c r="M14" s="7" t="n">
-        <v>46336</v>
+        <v>46276</v>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>180 days</t>
+          <t>120 days</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>VETERANS ADMIN (VA CCN)</t>
+          <t>AETNA</t>
         </is>
       </c>
       <c r="P14" s="6" t="n"/>
@@ -18338,7 +18366,7 @@
         <v>1</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>2493.33</v>
+        <v>7623.07</v>
       </c>
       <c r="U14" s="8" t="n">
         <v>0</v>
@@ -18346,25 +18374,21 @@
       <c r="V14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="6" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
+      <c r="W14" s="6" t="n"/>
       <c r="X14" s="8" t="n">
-        <v>2493.33</v>
+        <v>7623.07</v>
       </c>
       <c r="Y14" s="5" t="n">
         <v>86</v>
       </c>
       <c r="Z14" s="6" t="inlineStr">
         <is>
-          <t>M961</t>
+          <t>M48062</t>
         </is>
       </c>
       <c r="AA14" s="6" t="inlineStr">
         <is>
-          <t>T85122D</t>
+          <t>M5416</t>
         </is>
       </c>
       <c r="AB14" s="6" t="n"/>
@@ -18390,9 +18414,13 @@
           <t>ORTHO</t>
         </is>
       </c>
-      <c r="AI14" s="9" t="n"/>
+      <c r="AI14" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 120 days per contract.</t>
+        </is>
+      </c>
       <c r="AJ14" s="5" t="n">
-        <v>799</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="15">
@@ -18400,11 +18428,11 @@
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="5" t="n">
-        <v>559611258</v>
+        <v>559248529</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>HF400854650</t>
+          <t>HF551547091</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -18414,12 +18442,12 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Oscar Health</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Oscar Health</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -18429,7 +18457,7 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>63655</t>
+          <t>63685</t>
         </is>
       </c>
       <c r="K15" s="4" t="n"/>
@@ -18447,7 +18475,7 @@
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>VETERANS ADMIN (VA CCN)</t>
+          <t>OSCAR HEALTH</t>
         </is>
       </c>
       <c r="P15" s="6" t="n"/>
@@ -18457,7 +18485,7 @@
         <v>1</v>
       </c>
       <c r="T15" s="8" t="n">
-        <v>5784.24</v>
+        <v>2493.33</v>
       </c>
       <c r="U15" s="8" t="n">
         <v>0</v>
@@ -18467,41 +18495,37 @@
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
-          <t>06/11/2026</t>
+          <t>05/28/2026</t>
         </is>
       </c>
       <c r="X15" s="8" t="n">
-        <v>5784.24</v>
+        <v>2493.33</v>
       </c>
       <c r="Y15" s="5" t="n">
         <v>86</v>
       </c>
       <c r="Z15" s="6" t="inlineStr">
         <is>
-          <t>M961</t>
-        </is>
-      </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>T85122D</t>
-        </is>
-      </c>
+          <t>G90523</t>
+        </is>
+      </c>
+      <c r="AA15" s="6" t="n"/>
       <c r="AB15" s="6" t="n"/>
       <c r="AC15" s="6" t="n"/>
       <c r="AD15" s="5" t="n"/>
       <c r="AE15" s="6" t="inlineStr">
         <is>
-          <t>LUKE, TIMOTHY</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF15" s="6" t="inlineStr">
         <is>
-          <t>ASAP Surgery Centers North Valley LLC</t>
+          <t>Premier Endoscopy Center, LLC</t>
         </is>
       </c>
       <c r="AG15" s="6" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>05/15/2026</t>
         </is>
       </c>
       <c r="AH15" s="6" t="inlineStr">
@@ -18511,7 +18535,7 @@
       </c>
       <c r="AI15" s="9" t="n"/>
       <c r="AJ15" s="5" t="n">
-        <v>800</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16">
@@ -19588,7 +19612,7 @@
       </c>
       <c r="AI24" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ24" s="5" t="n">
@@ -19711,7 +19735,7 @@
       </c>
       <c r="AI25" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ25" s="5" t="n">
@@ -20739,7 +20763,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI2" s="9" t="n"/>
+      <c r="AI2" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ2" s="5" t="n">
         <v>745</v>
       </c>
@@ -20862,7 +20890,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI3" s="9" t="n"/>
+      <c r="AI3" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ3" s="5" t="n">
         <v>746</v>
       </c>
@@ -21721,7 +21753,7 @@
       </c>
       <c r="AI10" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ10" s="5" t="n">
@@ -21846,7 +21878,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI11" s="9" t="n"/>
+      <c r="AI11" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ11" s="5" t="n">
         <v>733</v>
       </c>
@@ -21973,7 +22009,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI12" s="9" t="n"/>
+      <c r="AI12" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ12" s="5" t="n">
         <v>558</v>
       </c>
@@ -22100,7 +22140,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI13" s="9" t="n"/>
+      <c r="AI13" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ13" s="5" t="n">
         <v>559</v>
       </c>
@@ -22217,7 +22261,7 @@
       </c>
       <c r="AI14" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ14" s="5" t="n">
@@ -22340,7 +22384,7 @@
       </c>
       <c r="AI15" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ15" s="5" t="n">
@@ -22463,7 +22507,7 @@
       </c>
       <c r="AI16" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ16" s="5" t="n">
@@ -24617,7 +24661,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI34" s="9" t="n"/>
+      <c r="AI34" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ34" s="5" t="n">
         <v>215</v>
       </c>
@@ -24744,7 +24792,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI35" s="9" t="n"/>
+      <c r="AI35" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ35" s="5" t="n">
         <v>216</v>
       </c>
@@ -25260,7 +25312,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI39" s="9" t="n"/>
+      <c r="AI39" s="9" t="inlineStr">
+        <is>
+          <t>AARP MA CHOICE / MEDICARE COMPLETE is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ39" s="5" t="n">
         <v>981</v>
       </c>
@@ -25377,7 +25433,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI40" s="9" t="n"/>
+      <c r="AI40" s="9" t="inlineStr">
+        <is>
+          <t>AARP MA CHOICE / MEDICARE COMPLETE is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ40" s="5" t="n">
         <v>982</v>
       </c>
@@ -25494,7 +25554,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI41" s="9" t="n"/>
+      <c r="AI41" s="9" t="inlineStr">
+        <is>
+          <t>AARP MA CHOICE / MEDICARE COMPLETE is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ41" s="5" t="n">
         <v>983</v>
       </c>
@@ -25592,14 +25656,14 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2 - Due in 6-30 days: 38</t>
+          <t xml:space="preserve">    2 - Due in 6-30 days: 40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3 - Due in 31+ days: 73</t>
+          <t xml:space="preserve">    3 - Due in 31+ days: 71</t>
         </is>
       </c>
     </row>

--- a/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-05 May - Specialty Claims.xlsx
@@ -27,10 +27,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="MM/DD/YYYY"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="MM/DD/YYYY"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -127,7 +126,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -282,12 +281,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -332,12 +331,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -382,12 +381,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -432,12 +431,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -482,12 +481,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -25599,7 +25598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -25739,7 +25738,7 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "25/06/2026";  Date Worked 1: "12/08/2026".</t>
+          <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Date Worked 1: "08/12/2026".</t>
         </is>
       </c>
     </row>
@@ -25756,46 +25755,39 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Both are real dates displayed DD/MM/YYYY. Processed Date is already filled in on the 13 claim lines whose Notes recorded one - the Note still carries the original wording, so nothing was lost. Date Worked 1 starts empty.</t>
+          <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Processed Date is already filled in on the 13 claim lines whose Notes recorded one - the Note still carries the original wording, so nothing was lost. Date Worked 1 starts empty.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Careful when typing into them: Excel reads what you type using its own date setting, not the DD/MM/YYYY the cell displays. On a US Excel, typing 06/25/2026 gives 25 June and the cell then shows 25/06/2026. Type the date the way your Excel expects it and let the cell do the formatting, or check the formula bar afterwards. Every other date column in these files is MM/DD/YYYY, as in the source data.</t>
-        </is>
-      </c>
+      <c r="A26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr"/>
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>How this file feeds the master</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>How this file feeds the master</t>
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 1,086 claim lines for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 1,086 claim lines for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
+          <t>The link is matched on Line ID (last column), not on row position, so sorting and filtering these sheets is safe. Do not edit or delete the Line ID column, and do not rename the specialty sheet tabs.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>The link is matched on Line ID (last column), not on row position, so sorting and filtering these sheets is safe. Do not edit or delete the Line ID column, and do not rename the specialty sheet tabs.</t>
-        </is>
-      </c>
+      <c r="A30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Everything else in this file is a static copy of the source data from 'Specialty Claims Pending 2026-S1.xlsx' (sheet 'Merged').</t>
         </is>
